--- a/database_sheets/purchased_products.xlsx
+++ b/database_sheets/purchased_products.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -604,9 +604,50 @@
         <v>22 Baker Street, London</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>mock_fbhru21wc</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-07-23T19:51:49.269Z</v>
+      </c>
+      <c r="C6" t="str">
+        <v>joh</v>
+      </c>
+      <c r="D6" t="str">
+        <v>john@example.com</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Gourmet Pizza Kitchen</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Margherita Pizza</v>
+      </c>
+      <c r="G6">
+        <v>14.99</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" t="str">
+        <v>14.99</v>
+      </c>
+      <c r="J6" t="str">
+        <v>cod</v>
+      </c>
+      <c r="K6" t="str">
+        <v>pending</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M6" t="str">
+        <v>21/10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M6"/>
   </ignoredErrors>
 </worksheet>
 </file>